--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="374">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -265,6 +265,9 @@
     <t>A type of a manufactured item that is used in the provision of healthcare without being substantially changed through that activity. The device may be a medical or non-medical device.</t>
   </si>
   <si>
+    <t>administrative.device</t>
+  </si>
+  <si>
     <t>Device.id</t>
   </si>
   <si>
@@ -348,7 +351,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -406,6 +409,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -446,7 +453,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -504,6 +511,10 @@
   </si>
   <si>
     <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>.id and .code</t>
@@ -686,7 +697,7 @@
     <t>Codes to identify how UDI data was entered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/udi-entry-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/udi-entry-type|4.3.0</t>
   </si>
   <si>
     <t>NA</t>
@@ -707,7 +718,7 @@
     <t>The availability status of the device.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/device-status|4.3.0</t>
   </si>
   <si>
     <t>.statusCode</t>
@@ -855,10 +866,10 @@
 </t>
   </si>
   <si>
-    <t>The name of the device</t>
-  </si>
-  <si>
-    <t>The name of the device.</t>
+    <t>The name that identifies the device</t>
+  </si>
+  <si>
+    <t>The name that identifies the device.</t>
   </si>
   <si>
     <t>Device.deviceName.type</t>
@@ -874,7 +885,7 @@
     <t>The type of name the device is referred by.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-nametype|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/device-nametype|4.3.0</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].code</t>
@@ -883,10 +894,10 @@
     <t>Device.modelNumber</t>
   </si>
   <si>
-    <t>The model number for the device</t>
-  </si>
-  <si>
-    <t>The model number for the device.</t>
+    <t>The manufacturer's model number for the device</t>
+  </si>
+  <si>
+    <t>The manufacturer's model number for the device.</t>
   </si>
   <si>
     <t>.softwareName (included as part)</t>
@@ -895,10 +906,10 @@
     <t>Device.partNumber</t>
   </si>
   <si>
-    <t>The part number of the device</t>
-  </si>
-  <si>
-    <t>The part number of the device.</t>
+    <t>The part number or catalog number of the device</t>
+  </si>
+  <si>
+    <t>The part number or catalog number of the device.</t>
   </si>
   <si>
     <t>Device.type</t>
@@ -976,10 +987,10 @@
     <t>Device.version.type</t>
   </si>
   <si>
-    <t>The type of the device version</t>
-  </si>
-  <si>
-    <t>The type of the device version.</t>
+    <t>The type of the device version, e.g. manufacturer, approved, internal</t>
+  </si>
+  <si>
+    <t>The type of the device version, e.g. manufacturer, approved, internal.</t>
   </si>
   <si>
     <t>Device.version.component</t>
@@ -1178,10 +1189,10 @@
 </t>
   </si>
   <si>
-    <t>The parent device</t>
-  </si>
-  <si>
-    <t>The parent device.</t>
+    <t>The device that this device is attached to or is part of</t>
+  </si>
+  <si>
+    <t>The device that this device is attached to or is part of.</t>
   </si>
 </sst>
 </file>
@@ -1763,7 +1774,7 @@
         <v>30</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>76</v>
@@ -1771,10 +1782,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1785,7 +1796,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>76</v>
@@ -1794,19 +1805,19 @@
         <v>76</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1856,13 +1867,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -1882,10 +1893,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1896,7 +1907,7 @@
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>76</v>
@@ -1905,16 +1916,16 @@
         <v>76</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1965,19 +1976,19 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -1991,10 +2002,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2005,28 +2016,28 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2076,19 +2087,19 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2102,10 +2113,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2116,7 +2127,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -2128,16 +2139,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2163,13 +2174,13 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -2187,19 +2198,19 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>76</v>
@@ -2213,21 +2224,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -2239,16 +2250,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2298,22 +2309,22 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>76</v>
@@ -2324,14 +2335,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2350,16 +2361,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2409,7 +2420,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2421,10 +2432,10 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>76</v>
@@ -2435,14 +2446,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2461,16 +2472,16 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2520,7 +2531,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2532,10 +2543,10 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>76</v>
@@ -2546,14 +2557,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2566,25 +2577,25 @@
         <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2633,7 +2644,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2645,10 +2656,10 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>76</v>
@@ -2659,10 +2670,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2685,16 +2696,16 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2744,7 +2755,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2756,24 +2767,24 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2784,7 +2795,7 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>76</v>
@@ -2796,13 +2807,13 @@
         <v>76</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2853,19 +2864,19 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>76</v>
@@ -2879,10 +2890,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2902,19 +2913,19 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2964,7 +2975,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2976,13 +2987,13 @@
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>76</v>
@@ -2990,10 +3001,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3004,7 +3015,7 @@
         <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>76</v>
@@ -3016,13 +3027,13 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3073,13 +3084,13 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>76</v>
@@ -3088,7 +3099,7 @@
         <v>76</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
@@ -3099,14 +3110,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3125,16 +3136,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3184,7 +3195,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3196,10 +3207,10 @@
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -3210,14 +3221,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3230,25 +3241,25 @@
         <v>76</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3297,7 +3308,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3309,10 +3320,10 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3323,21 +3334,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
@@ -3346,16 +3357,16 @@
         <v>76</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3406,47 +3417,47 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -3458,13 +3469,13 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3515,36 +3526,36 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3555,7 +3566,7 @@
         <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>76</v>
@@ -3567,17 +3578,17 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3626,22 +3637,22 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -3652,21 +3663,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>76</v>
@@ -3675,19 +3686,19 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3737,47 +3748,47 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>76</v>
@@ -3786,19 +3797,19 @@
         <v>76</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3848,36 +3859,36 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3888,7 +3899,7 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>76</v>
@@ -3900,17 +3911,17 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3935,13 +3946,13 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>76</v>
@@ -3959,22 +3970,22 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
@@ -3985,10 +3996,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3999,28 +4010,28 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4046,13 +4057,13 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>76</v>
@@ -4070,25 +4081,25 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4096,10 +4107,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4122,13 +4133,13 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4155,13 +4166,13 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4179,7 +4190,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4191,13 +4202,13 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>76</v>
@@ -4205,21 +4216,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
@@ -4231,16 +4242,16 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4290,36 +4301,36 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4330,7 +4341,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -4342,13 +4353,13 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4399,36 +4410,36 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4439,7 +4450,7 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
@@ -4451,13 +4462,13 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4508,36 +4519,36 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4548,7 +4559,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4560,13 +4571,13 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4617,36 +4628,36 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4657,7 +4668,7 @@
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -4669,13 +4680,13 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4726,36 +4737,36 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4766,7 +4777,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -4778,16 +4789,16 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4837,25 +4848,25 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>76</v>
@@ -4863,10 +4874,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4874,10 +4885,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>76</v>
@@ -4889,13 +4900,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4946,7 +4957,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4958,7 +4969,7 @@
         <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>76</v>
@@ -4972,10 +4983,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4986,7 +4997,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
@@ -4998,13 +5009,13 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5055,13 +5066,13 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
@@ -5070,7 +5081,7 @@
         <v>76</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>76</v>
@@ -5081,14 +5092,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5107,16 +5118,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5166,7 +5177,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5178,10 +5189,10 @@
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5192,14 +5203,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5212,25 +5223,25 @@
         <v>76</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -5279,7 +5290,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5291,10 +5302,10 @@
         <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5305,21 +5316,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>76</v>
@@ -5331,13 +5342,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5388,19 +5399,19 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>76</v>
@@ -5414,10 +5425,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5425,10 +5436,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>76</v>
@@ -5440,13 +5451,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5473,49 +5484,49 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="AG36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>76</v>
@@ -5523,10 +5534,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5537,7 +5548,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -5549,13 +5560,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5606,25 +5617,25 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>76</v>
@@ -5632,10 +5643,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5646,7 +5657,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>
@@ -5658,16 +5669,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5717,25 +5728,25 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>76</v>
@@ -5743,10 +5754,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5757,7 +5768,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
@@ -5769,13 +5780,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5802,43 +5813,43 @@
         <v>76</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="Y39" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>279</v>
-      </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
@@ -5852,10 +5863,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5878,13 +5889,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5935,7 +5946,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5947,7 +5958,7 @@
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
@@ -5961,10 +5972,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5975,7 +5986,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>76</v>
@@ -5987,13 +5998,13 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6044,13 +6055,13 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>76</v>
@@ -6059,7 +6070,7 @@
         <v>76</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
@@ -6070,14 +6081,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6096,16 +6107,16 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6155,7 +6166,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6167,10 +6178,10 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
@@ -6181,14 +6192,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6201,25 +6212,25 @@
         <v>76</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6268,7 +6279,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6280,10 +6291,10 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6294,21 +6305,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -6320,13 +6331,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6377,19 +6388,19 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>76</v>
@@ -6403,10 +6414,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6417,7 +6428,7 @@
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>76</v>
@@ -6429,13 +6440,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6486,25 +6497,25 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>76</v>
@@ -6512,10 +6523,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6538,13 +6549,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6595,7 +6606,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6607,7 +6618,7 @@
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>76</v>
@@ -6621,10 +6632,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6635,7 +6646,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>76</v>
@@ -6647,13 +6658,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6704,13 +6715,13 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
@@ -6719,7 +6730,7 @@
         <v>76</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
@@ -6730,14 +6741,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6756,16 +6767,16 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6815,7 +6826,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6827,10 +6838,10 @@
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
@@ -6841,14 +6852,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6861,25 +6872,25 @@
         <v>76</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -6928,7 +6939,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6940,10 +6951,10 @@
         <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
@@ -6954,21 +6965,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>76</v>
@@ -6980,13 +6991,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7037,19 +7048,19 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>76</v>
@@ -7063,10 +7074,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7077,7 +7088,7 @@
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>76</v>
@@ -7089,13 +7100,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7146,25 +7157,25 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>76</v>
@@ -7172,10 +7183,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7183,10 +7194,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>76</v>
@@ -7198,13 +7209,13 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7255,19 +7266,19 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>76</v>
@@ -7281,10 +7292,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7307,13 +7318,13 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7364,7 +7375,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7376,7 +7387,7 @@
         <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>76</v>
@@ -7390,10 +7401,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7404,7 +7415,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>76</v>
@@ -7416,13 +7427,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7473,13 +7484,13 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>76</v>
@@ -7488,7 +7499,7 @@
         <v>76</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -7499,14 +7510,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7525,16 +7536,16 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7584,7 +7595,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7596,10 +7607,10 @@
         <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7610,14 +7621,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7630,25 +7641,25 @@
         <v>76</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -7697,7 +7708,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7709,10 +7720,10 @@
         <v>76</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
@@ -7723,10 +7734,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7734,10 +7745,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>76</v>
@@ -7749,13 +7760,13 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7806,19 +7817,19 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>76</v>
@@ -7832,10 +7843,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7858,13 +7869,13 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7915,7 +7926,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -7927,7 +7938,7 @@
         <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>76</v>
@@ -7941,10 +7952,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7967,13 +7978,13 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8024,7 +8035,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8036,7 +8047,7 @@
         <v>76</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>76</v>
@@ -8050,10 +8061,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8064,7 +8075,7 @@
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>76</v>
@@ -8076,17 +8087,17 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8135,25 +8146,25 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>76</v>
@@ -8161,10 +8172,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8175,7 +8186,7 @@
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>76</v>
@@ -8187,13 +8198,13 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8244,25 +8255,25 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>76</v>
@@ -8270,10 +8281,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8296,16 +8307,16 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8355,7 +8366,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8367,13 +8378,13 @@
         <v>76</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>76</v>
@@ -8381,10 +8392,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8395,7 +8406,7 @@
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>76</v>
@@ -8407,17 +8418,17 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -8466,25 +8477,25 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>76</v>
@@ -8492,10 +8503,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8506,7 +8517,7 @@
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>76</v>
@@ -8518,16 +8529,16 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8577,25 +8588,25 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>76</v>
@@ -8603,10 +8614,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8620,7 +8631,7 @@
         <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>76</v>
@@ -8629,13 +8640,13 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8686,7 +8697,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8698,10 +8709,10 @@
         <v>76</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -8712,10 +8723,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8735,16 +8746,16 @@
         <v>76</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8795,7 +8806,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -8807,10 +8818,10 @@
         <v>76</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>76</v>
@@ -8821,10 +8832,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8835,7 +8846,7 @@
         <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>76</v>
@@ -8847,13 +8858,13 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8904,19 +8915,19 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>76</v>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="371">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -265,9 +265,6 @@
     <t>A type of a manufactured item that is used in the provision of healthcare without being substantially changed through that activity. The device may be a medical or non-medical device.</t>
   </si>
   <si>
-    <t>administrative.device</t>
-  </si>
-  <si>
     <t>Device.id</t>
   </si>
   <si>
@@ -351,7 +348,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -409,10 +406,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -453,7 +446,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -511,10 +504,6 @@
   </si>
   <si>
     <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>.id and .code</t>
@@ -697,7 +686,7 @@
     <t>Codes to identify how UDI data was entered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/udi-entry-type|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/udi-entry-type|4.0.1</t>
   </si>
   <si>
     <t>NA</t>
@@ -718,7 +707,7 @@
     <t>The availability status of the device.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/device-status|4.0.1</t>
   </si>
   <si>
     <t>.statusCode</t>
@@ -866,10 +855,10 @@
 </t>
   </si>
   <si>
-    <t>The name that identifies the device</t>
-  </si>
-  <si>
-    <t>The name that identifies the device.</t>
+    <t>The name of the device</t>
+  </si>
+  <si>
+    <t>The name of the device.</t>
   </si>
   <si>
     <t>Device.deviceName.type</t>
@@ -885,7 +874,7 @@
     <t>The type of name the device is referred by.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-nametype|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/device-nametype|4.0.1</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].code</t>
@@ -894,10 +883,10 @@
     <t>Device.modelNumber</t>
   </si>
   <si>
-    <t>The manufacturer's model number for the device</t>
-  </si>
-  <si>
-    <t>The manufacturer's model number for the device.</t>
+    <t>The model number for the device</t>
+  </si>
+  <si>
+    <t>The model number for the device.</t>
   </si>
   <si>
     <t>.softwareName (included as part)</t>
@@ -906,10 +895,10 @@
     <t>Device.partNumber</t>
   </si>
   <si>
-    <t>The part number or catalog number of the device</t>
-  </si>
-  <si>
-    <t>The part number or catalog number of the device.</t>
+    <t>The part number of the device</t>
+  </si>
+  <si>
+    <t>The part number of the device.</t>
   </si>
   <si>
     <t>Device.type</t>
@@ -987,10 +976,10 @@
     <t>Device.version.type</t>
   </si>
   <si>
-    <t>The type of the device version, e.g. manufacturer, approved, internal</t>
-  </si>
-  <si>
-    <t>The type of the device version, e.g. manufacturer, approved, internal.</t>
+    <t>The type of the device version</t>
+  </si>
+  <si>
+    <t>The type of the device version.</t>
   </si>
   <si>
     <t>Device.version.component</t>
@@ -1189,10 +1178,10 @@
 </t>
   </si>
   <si>
-    <t>The device that this device is attached to or is part of</t>
-  </si>
-  <si>
-    <t>The device that this device is attached to or is part of.</t>
+    <t>The parent device</t>
+  </si>
+  <si>
+    <t>The parent device.</t>
   </si>
 </sst>
 </file>
@@ -1774,7 +1763,7 @@
         <v>30</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>76</v>
@@ -1782,10 +1771,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1796,28 +1785,28 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1867,13 +1856,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -1893,10 +1882,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1907,25 +1896,25 @@
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1976,19 +1965,19 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -2002,10 +1991,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2016,28 +2005,28 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2087,19 +2076,19 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2113,10 +2102,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2127,7 +2116,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -2139,16 +2128,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2174,43 +2163,43 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>111</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>76</v>
@@ -2224,21 +2213,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -2250,16 +2239,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2309,22 +2298,22 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK7" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>76</v>
@@ -2335,14 +2324,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2361,16 +2350,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2420,7 +2409,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2432,10 +2421,10 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>76</v>
@@ -2446,14 +2435,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2472,16 +2461,16 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2531,7 +2520,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2543,10 +2532,10 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>76</v>
@@ -2557,14 +2546,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2577,25 +2566,25 @@
         <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2644,7 +2633,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2656,10 +2645,10 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>76</v>
@@ -2670,10 +2659,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2696,16 +2685,16 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2755,7 +2744,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2767,24 +2756,24 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>149</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2795,7 +2784,7 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>76</v>
@@ -2807,13 +2796,13 @@
         <v>76</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2864,19 +2853,19 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>76</v>
@@ -2890,10 +2879,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2913,19 +2902,19 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2975,7 +2964,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2987,13 +2976,13 @@
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>76</v>
@@ -3001,10 +2990,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3015,7 +3004,7 @@
         <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>76</v>
@@ -3027,13 +3016,13 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3084,13 +3073,13 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>76</v>
@@ -3099,7 +3088,7 @@
         <v>76</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
@@ -3110,14 +3099,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3136,16 +3125,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3195,7 +3184,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3207,10 +3196,10 @@
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -3221,14 +3210,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3241,25 +3230,25 @@
         <v>76</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3308,7 +3297,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3320,10 +3309,10 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3334,39 +3323,39 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3417,47 +3406,47 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -3469,13 +3458,13 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3526,36 +3515,36 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3566,7 +3555,7 @@
         <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>76</v>
@@ -3578,17 +3567,17 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3637,22 +3626,22 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -3663,42 +3652,42 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3748,68 +3737,68 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3859,36 +3848,36 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3899,7 +3888,7 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>76</v>
@@ -3911,17 +3900,17 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -3946,46 +3935,46 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
@@ -3996,10 +3985,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4010,28 +3999,28 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I23" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4057,49 +4046,49 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4107,10 +4096,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4133,13 +4122,13 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4166,13 +4155,13 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4190,7 +4179,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4202,13 +4191,13 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>76</v>
@@ -4216,21 +4205,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
@@ -4242,16 +4231,16 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4301,36 +4290,36 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4341,7 +4330,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -4353,13 +4342,13 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4410,36 +4399,36 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="AL26" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4450,7 +4439,7 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
@@ -4462,13 +4451,13 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4519,36 +4508,36 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4559,7 +4548,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4571,13 +4560,13 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4628,36 +4617,36 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="AL28" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4668,7 +4657,7 @@
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -4680,13 +4669,13 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4737,36 +4726,36 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4777,7 +4766,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -4789,16 +4778,16 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4848,25 +4837,25 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>76</v>
@@ -4874,10 +4863,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4885,10 +4874,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>76</v>
@@ -4900,13 +4889,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4957,7 +4946,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4969,7 +4958,7 @@
         <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>76</v>
@@ -4983,10 +4972,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4997,7 +4986,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
@@ -5009,13 +4998,13 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5066,13 +5055,13 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
@@ -5081,7 +5070,7 @@
         <v>76</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>76</v>
@@ -5092,14 +5081,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5118,16 +5107,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5177,7 +5166,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5189,10 +5178,10 @@
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5203,14 +5192,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5223,25 +5212,25 @@
         <v>76</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -5290,7 +5279,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5302,10 +5291,10 @@
         <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5316,21 +5305,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>76</v>
@@ -5342,13 +5331,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5399,19 +5388,19 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>76</v>
@@ -5425,10 +5414,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5436,10 +5425,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>76</v>
@@ -5451,13 +5440,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5484,13 +5473,13 @@
         <v>76</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5508,25 +5497,25 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>76</v>
@@ -5534,10 +5523,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5548,7 +5537,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -5560,13 +5549,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5617,25 +5606,25 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK37" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AG37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="AL37" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>76</v>
@@ -5643,10 +5632,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5657,7 +5646,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>
@@ -5669,16 +5658,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5728,25 +5717,25 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>76</v>
@@ -5754,10 +5743,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5768,7 +5757,7 @@
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
@@ -5780,13 +5769,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5813,13 +5802,13 @@
         <v>76</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>76</v>
@@ -5837,19 +5826,19 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
@@ -5863,10 +5852,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5889,13 +5878,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5946,7 +5935,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5958,7 +5947,7 @@
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
@@ -5972,10 +5961,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5986,7 +5975,7 @@
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>76</v>
@@ -5998,13 +5987,13 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6055,13 +6044,13 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>76</v>
@@ -6070,7 +6059,7 @@
         <v>76</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
@@ -6081,14 +6070,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6107,16 +6096,16 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6166,7 +6155,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6178,10 +6167,10 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
@@ -6192,14 +6181,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6212,25 +6201,25 @@
         <v>76</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6279,7 +6268,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6291,10 +6280,10 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6305,21 +6294,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -6331,13 +6320,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6388,19 +6377,19 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>76</v>
@@ -6414,10 +6403,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6428,7 +6417,7 @@
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>76</v>
@@ -6440,13 +6429,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6497,25 +6486,25 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>76</v>
@@ -6523,10 +6512,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6549,13 +6538,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6606,7 +6595,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6618,7 +6607,7 @@
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>76</v>
@@ -6632,10 +6621,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6646,7 +6635,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>76</v>
@@ -6658,13 +6647,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6715,13 +6704,13 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
@@ -6730,7 +6719,7 @@
         <v>76</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
@@ -6741,14 +6730,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6767,16 +6756,16 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6826,7 +6815,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6838,10 +6827,10 @@
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
@@ -6852,14 +6841,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6872,25 +6861,25 @@
         <v>76</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -6939,7 +6928,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6951,10 +6940,10 @@
         <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
@@ -6965,21 +6954,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>76</v>
@@ -6991,13 +6980,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7048,19 +7037,19 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>76</v>
@@ -7074,10 +7063,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7088,7 +7077,7 @@
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>76</v>
@@ -7100,13 +7089,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7157,25 +7146,25 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>76</v>
@@ -7183,10 +7172,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7194,10 +7183,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>76</v>
@@ -7209,13 +7198,13 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7266,19 +7255,19 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>76</v>
@@ -7292,10 +7281,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7318,13 +7307,13 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7375,7 +7364,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7387,7 +7376,7 @@
         <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>76</v>
@@ -7401,10 +7390,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7415,7 +7404,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>76</v>
@@ -7427,13 +7416,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7484,13 +7473,13 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>76</v>
@@ -7499,7 +7488,7 @@
         <v>76</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -7510,14 +7499,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7536,16 +7525,16 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7595,7 +7584,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7607,10 +7596,10 @@
         <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7621,14 +7610,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7641,25 +7630,25 @@
         <v>76</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -7708,7 +7697,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7720,10 +7709,10 @@
         <v>76</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
@@ -7734,10 +7723,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7745,10 +7734,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>76</v>
@@ -7760,13 +7749,13 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7817,19 +7806,19 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>76</v>
@@ -7843,10 +7832,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7869,13 +7858,13 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7926,7 +7915,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -7938,7 +7927,7 @@
         <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>76</v>
@@ -7952,10 +7941,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7978,13 +7967,13 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8035,7 +8024,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8047,7 +8036,7 @@
         <v>76</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>76</v>
@@ -8061,10 +8050,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8075,7 +8064,7 @@
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>76</v>
@@ -8087,17 +8076,17 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8146,25 +8135,25 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>76</v>
@@ -8172,10 +8161,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8186,7 +8175,7 @@
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>76</v>
@@ -8198,13 +8187,13 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8255,25 +8244,25 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>76</v>
@@ -8281,10 +8270,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8307,16 +8296,16 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8366,7 +8355,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8378,13 +8367,13 @@
         <v>76</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>76</v>
@@ -8392,10 +8381,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8406,7 +8395,7 @@
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>76</v>
@@ -8418,17 +8407,17 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -8477,25 +8466,25 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>76</v>
@@ -8503,10 +8492,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8517,7 +8506,7 @@
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>76</v>
@@ -8529,16 +8518,16 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8588,25 +8577,25 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>76</v>
@@ -8614,10 +8603,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8631,7 +8620,7 @@
         <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>76</v>
@@ -8640,13 +8629,13 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8697,7 +8686,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8709,10 +8698,10 @@
         <v>76</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -8723,10 +8712,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8746,16 +8735,16 @@
         <v>76</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8806,7 +8795,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -8818,10 +8807,10 @@
         <v>76</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>76</v>
@@ -8832,10 +8821,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8846,7 +8835,7 @@
         <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>76</v>
@@ -8858,13 +8847,13 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8915,19 +8904,19 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>76</v>

--- a/branches/Richard/StructureDefinition-device-for-testing.xlsx
+++ b/branches/Richard/StructureDefinition-device-for-testing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
